--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ31"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3138,10 +3138,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111958182</v>
+        <v>136809697</v>
       </c>
       <c r="B24" t="n">
-        <v>57132</v>
+        <v>58005</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3168,27 +3168,24 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Österåsen, Österås, Ång</t>
+          <t>Ådalsleden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609747</v>
+        <v>609858</v>
       </c>
       <c r="R24" t="n">
-        <v>7011953</v>
+        <v>7012149</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3215,17 +3212,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>1K</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3240,74 +3242,74 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lennart Vessberg</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lennart Vessberg</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111958182</t>
+          <t>https://artportalen.se/Sighting/136809697</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111958205</v>
+        <v>111958182</v>
       </c>
       <c r="B25" t="n">
-        <v>99118</v>
+        <v>57132</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Österåsen, Ång</t>
+          <t>Österåsen, Österås, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609803</v>
+        <v>609747</v>
       </c>
       <c r="R25" t="n">
-        <v>7011969</v>
+        <v>7011953</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3344,7 +3346,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>½ m2</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3353,7 +3355,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3371,16 +3372,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111958205</t>
+          <t>https://artportalen.se/Sighting/111958182</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104730081</v>
+        <v>111958205</v>
       </c>
       <c r="B26" t="n">
-        <v>79328</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3388,38 +3389,49 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>230405</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Österåsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609902</v>
+        <v>609803</v>
       </c>
       <c r="R26" t="n">
-        <v>7012011</v>
+        <v>7011969</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3443,22 +3455,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>½ m2</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3467,30 +3474,31 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Lennart Vessberg</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Lennart Vessberg</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730081</t>
+          <t>https://artportalen.se/Sighting/111958205</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104730336</v>
+        <v>104730081</v>
       </c>
       <c r="B27" t="n">
         <v>79328</v>
@@ -3526,10 +3534,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609883</v>
+        <v>609902</v>
       </c>
       <c r="R27" t="n">
-        <v>7012110</v>
+        <v>7012011</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3597,13 +3605,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730336</t>
+          <t>https://artportalen.se/Sighting/104730081</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>104730419</v>
+        <v>104730336</v>
       </c>
       <c r="B28" t="n">
         <v>79328</v>
@@ -3639,10 +3647,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609955</v>
+        <v>609883</v>
       </c>
       <c r="R28" t="n">
-        <v>7012162</v>
+        <v>7012110</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3710,13 +3718,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730419</t>
+          <t>https://artportalen.se/Sighting/104730336</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>104730461</v>
+        <v>104730419</v>
       </c>
       <c r="B29" t="n">
         <v>79328</v>
@@ -3752,10 +3760,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609975</v>
+        <v>609955</v>
       </c>
       <c r="R29" t="n">
-        <v>7012174</v>
+        <v>7012162</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3823,13 +3831,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730461</t>
+          <t>https://artportalen.se/Sighting/104730419</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104730483</v>
+        <v>104730461</v>
       </c>
       <c r="B30" t="n">
         <v>79328</v>
@@ -3865,10 +3873,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609999</v>
+        <v>609975</v>
       </c>
       <c r="R30" t="n">
-        <v>7012162</v>
+        <v>7012174</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3936,13 +3944,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730483</t>
+          <t>https://artportalen.se/Sighting/104730461</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>104730501</v>
+        <v>104730483</v>
       </c>
       <c r="B31" t="n">
         <v>79328</v>
@@ -3978,10 +3986,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>610046</v>
+        <v>609999</v>
       </c>
       <c r="R31" t="n">
-        <v>7012129</v>
+        <v>7012162</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4048,6 +4056,119 @@
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104730483</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>104730501</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>610046</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7012129</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/104730501</t>
         </is>
@@ -4085,6 +4206,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3498,49 +3498,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104730081</v>
+        <v>136809946</v>
       </c>
       <c r="B27" t="n">
-        <v>79328</v>
+        <v>98404</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>230405</v>
+        <v>223358</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Ådalsleden, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609902</v>
+        <v>609858</v>
       </c>
       <c r="R27" t="n">
-        <v>7012011</v>
+        <v>7012149</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3564,22 +3563,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3594,24 +3593,24 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730081</t>
+          <t>https://artportalen.se/Sighting/136809946</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>104730336</v>
+        <v>104730081</v>
       </c>
       <c r="B28" t="n">
         <v>79328</v>
@@ -3647,10 +3646,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609883</v>
+        <v>609902</v>
       </c>
       <c r="R28" t="n">
-        <v>7012110</v>
+        <v>7012011</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3718,13 +3717,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730336</t>
+          <t>https://artportalen.se/Sighting/104730081</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>104730419</v>
+        <v>104730336</v>
       </c>
       <c r="B29" t="n">
         <v>79328</v>
@@ -3760,10 +3759,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609955</v>
+        <v>609883</v>
       </c>
       <c r="R29" t="n">
-        <v>7012162</v>
+        <v>7012110</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3831,13 +3830,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730419</t>
+          <t>https://artportalen.se/Sighting/104730336</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104730461</v>
+        <v>104730419</v>
       </c>
       <c r="B30" t="n">
         <v>79328</v>
@@ -3873,10 +3872,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609975</v>
+        <v>609955</v>
       </c>
       <c r="R30" t="n">
-        <v>7012174</v>
+        <v>7012162</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3944,13 +3943,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730461</t>
+          <t>https://artportalen.se/Sighting/104730419</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>104730483</v>
+        <v>104730461</v>
       </c>
       <c r="B31" t="n">
         <v>79328</v>
@@ -3986,10 +3985,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609999</v>
+        <v>609975</v>
       </c>
       <c r="R31" t="n">
-        <v>7012162</v>
+        <v>7012174</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4057,13 +4056,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730483</t>
+          <t>https://artportalen.se/Sighting/104730461</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>104730501</v>
+        <v>104730483</v>
       </c>
       <c r="B32" t="n">
         <v>79328</v>
@@ -4099,10 +4098,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>610046</v>
+        <v>609999</v>
       </c>
       <c r="R32" t="n">
-        <v>7012129</v>
+        <v>7012162</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4169,6 +4168,119 @@
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104730483</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>104730501</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>610046</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7012129</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/104730501</t>
         </is>
@@ -4207,6 +4319,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ33"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2911,10 +2911,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111958248</v>
+        <v>137031412</v>
       </c>
       <c r="B22" t="n">
-        <v>89156</v>
+        <v>93413</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2922,45 +2922,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4412</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Österåsen, Ång</t>
+          <t>Ådalsleden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>609824</v>
+        <v>609978</v>
       </c>
       <c r="R22" t="n">
-        <v>7011907</v>
+        <v>7012114</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2987,12 +2976,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3001,73 +3000,82 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lennart Vessberg</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lennart Vessberg</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111958248</t>
+          <t>https://artportalen.se/Sighting/137031412</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104730200</v>
+        <v>111958248</v>
       </c>
       <c r="B23" t="n">
-        <v>79327</v>
+        <v>89156</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Österåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609910</v>
+        <v>609824</v>
       </c>
       <c r="R23" t="n">
-        <v>7012030</v>
+        <v>7011907</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3091,22 +3099,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>09:29</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3115,80 +3113,73 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Lennart Vessberg</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Lennart Vessberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730200</t>
+          <t>https://artportalen.se/Sighting/111958248</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136809697</v>
+        <v>104730200</v>
       </c>
       <c r="B24" t="n">
-        <v>58005</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ådalsleden, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609858</v>
+        <v>609910</v>
       </c>
       <c r="R24" t="n">
-        <v>7012149</v>
+        <v>7012030</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3212,22 +3203,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2022-11-18</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2022-11-18</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3242,27 +3233,27 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136809697</t>
+          <t>https://artportalen.se/Sighting/104730200</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111958182</v>
+        <v>136809697</v>
       </c>
       <c r="B25" t="n">
-        <v>57132</v>
+        <v>58005</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,16 +3261,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3289,27 +3280,24 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Österåsen, Österås, Ång</t>
+          <t>Ådalsleden, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609747</v>
+        <v>609858</v>
       </c>
       <c r="R25" t="n">
-        <v>7011953</v>
+        <v>7012149</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3336,17 +3324,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>1K</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3361,74 +3354,74 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lennart Vessberg</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lennart Vessberg</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111958182</t>
+          <t>https://artportalen.se/Sighting/136809697</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111958205</v>
+        <v>111958182</v>
       </c>
       <c r="B26" t="n">
-        <v>99118</v>
+        <v>57132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Österåsen, Ång</t>
+          <t>Österåsen, Österås, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609803</v>
+        <v>609747</v>
       </c>
       <c r="R26" t="n">
-        <v>7011969</v>
+        <v>7011953</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3465,7 +3458,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>½ m2</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3474,7 +3467,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3492,51 +3484,63 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111958205</t>
+          <t>https://artportalen.se/Sighting/111958182</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136809946</v>
+        <v>111958205</v>
       </c>
       <c r="B27" t="n">
-        <v>98404</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ådalsleden, Ång</t>
+          <t>Österåsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609858</v>
+        <v>609803</v>
       </c>
       <c r="R27" t="n">
-        <v>7012149</v>
+        <v>7011969</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3563,22 +3567,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>½ m2</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,72 +3586,72 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Lennart Vessberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Lennart Vessberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136809946</t>
+          <t>https://artportalen.se/Sighting/111958205</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>104730081</v>
+        <v>136809946</v>
       </c>
       <c r="B28" t="n">
-        <v>79328</v>
+        <v>98410</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>230405</v>
+        <v>223358</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Ådalsleden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609902</v>
+        <v>609858</v>
       </c>
       <c r="R28" t="n">
-        <v>7012011</v>
+        <v>7012149</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3676,22 +3675,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3706,66 +3705,65 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730081</t>
+          <t>https://artportalen.se/Sighting/136809946</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>104730336</v>
+        <v>137031347</v>
       </c>
       <c r="B29" t="n">
-        <v>79328</v>
+        <v>79164</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>230405</v>
+        <v>228659</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Fönsterlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Cladonia stellaris</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Ådalsleden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609883</v>
+        <v>609978</v>
       </c>
       <c r="R29" t="n">
-        <v>7012110</v>
+        <v>7012114</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3789,22 +3787,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3819,24 +3817,24 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730336</t>
+          <t>https://artportalen.se/Sighting/137031347</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104730419</v>
+        <v>104730081</v>
       </c>
       <c r="B30" t="n">
         <v>79328</v>
@@ -3872,10 +3870,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609955</v>
+        <v>609902</v>
       </c>
       <c r="R30" t="n">
-        <v>7012162</v>
+        <v>7012011</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3943,13 +3941,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730419</t>
+          <t>https://artportalen.se/Sighting/104730081</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>104730461</v>
+        <v>104730336</v>
       </c>
       <c r="B31" t="n">
         <v>79328</v>
@@ -3985,10 +3983,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609975</v>
+        <v>609883</v>
       </c>
       <c r="R31" t="n">
-        <v>7012174</v>
+        <v>7012110</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4056,13 +4054,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730461</t>
+          <t>https://artportalen.se/Sighting/104730336</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>104730483</v>
+        <v>104730419</v>
       </c>
       <c r="B32" t="n">
         <v>79328</v>
@@ -4098,7 +4096,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609999</v>
+        <v>609955</v>
       </c>
       <c r="R32" t="n">
         <v>7012162</v>
@@ -4169,13 +4167,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730483</t>
+          <t>https://artportalen.se/Sighting/104730419</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>104730501</v>
+        <v>104730461</v>
       </c>
       <c r="B33" t="n">
         <v>79328</v>
@@ -4211,10 +4209,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>610046</v>
+        <v>609975</v>
       </c>
       <c r="R33" t="n">
-        <v>7012129</v>
+        <v>7012174</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4281,6 +4279,232 @@
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104730461</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>104730483</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>609999</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7012162</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104730483</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>104730501</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>610046</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7012129</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/104730501</t>
         </is>
@@ -4320,6 +4544,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -2914,7 +2914,7 @@
         <v>137031412</v>
       </c>
       <c r="B22" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>136809946</v>
       </c>
       <c r="B28" t="n">
-        <v>98410</v>
+        <v>98412</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>137031347</v>
       </c>
       <c r="B29" t="n">
-        <v>79164</v>
+        <v>79166</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -2914,7 +2914,7 @@
         <v>137031412</v>
       </c>
       <c r="B22" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>136809946</v>
       </c>
       <c r="B28" t="n">
-        <v>98412</v>
+        <v>98413</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3725,7 +3725,7 @@
         <v>137031347</v>
       </c>
       <c r="B29" t="n">
-        <v>79166</v>
+        <v>79167</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ35"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2914,7 +2914,7 @@
         <v>137031412</v>
       </c>
       <c r="B22" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3371,10 +3371,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>111958182</v>
+        <v>137117586</v>
       </c>
       <c r="B26" t="n">
-        <v>57132</v>
+        <v>58000</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3382,46 +3382,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>100110</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>J.F. Gmelin, 1788</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Österåsen, Österås, Ång</t>
+          <t>Ådalsleden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>609747</v>
+        <v>609978</v>
       </c>
       <c r="R26" t="n">
-        <v>7011953</v>
+        <v>7012114</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3448,17 +3448,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-09-04</t>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1K</t>
+          <t>2 individer som rörde sig i och utanför Österåsenskogens naturreservat en lång stund. Mycket läten.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3473,74 +3483,74 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lennart Vessberg</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lennart Vessberg</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111958182</t>
+          <t>https://artportalen.se/Sighting/137117586</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111958205</v>
+        <v>111958182</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>57132</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Österåsen, Ång</t>
+          <t>Österåsen, Österås, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609803</v>
+        <v>609747</v>
       </c>
       <c r="R27" t="n">
-        <v>7011969</v>
+        <v>7011953</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3577,7 +3587,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>½ m2</t>
+          <t>1K</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3586,7 +3596,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3604,51 +3613,63 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111958205</t>
+          <t>https://artportalen.se/Sighting/111958182</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136809946</v>
+        <v>111958205</v>
       </c>
       <c r="B28" t="n">
-        <v>98413</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>223358</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ådalsleden, Ång</t>
+          <t>Österåsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609858</v>
+        <v>609803</v>
       </c>
       <c r="R28" t="n">
-        <v>7012149</v>
+        <v>7011969</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3675,22 +3696,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2023-09-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>½ m2</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3699,33 +3715,34 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Lennart Vessberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Sofia Möller Skog</t>
+          <t>Lennart Vessberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136809946</t>
+          <t>https://artportalen.se/Sighting/111958205</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>137031347</v>
+        <v>136809946</v>
       </c>
       <c r="B29" t="n">
-        <v>79167</v>
+        <v>98419</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3733,21 +3750,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228659</v>
+        <v>223358</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fönsterlav</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia stellaris</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Opiz) Pouzar &amp; Vezda</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3757,10 +3774,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609978</v>
+        <v>609858</v>
       </c>
       <c r="R29" t="n">
-        <v>7012114</v>
+        <v>7012149</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3787,22 +3804,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3828,55 +3845,54 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137031347</t>
+          <t>https://artportalen.se/Sighting/136809946</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104730081</v>
+        <v>137031347</v>
       </c>
       <c r="B30" t="n">
-        <v>79328</v>
+        <v>79167</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>230405</v>
+        <v>228659</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Fönsterlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Cladonia stellaris</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Ådalsleden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>609902</v>
+        <v>609978</v>
       </c>
       <c r="R30" t="n">
-        <v>7012011</v>
+        <v>7012114</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3900,22 +3916,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3930,24 +3946,24 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Sofia Möller Skog</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730081</t>
+          <t>https://artportalen.se/Sighting/137031347</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>104730336</v>
+        <v>104730081</v>
       </c>
       <c r="B31" t="n">
         <v>79328</v>
@@ -3983,10 +3999,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>609883</v>
+        <v>609902</v>
       </c>
       <c r="R31" t="n">
-        <v>7012110</v>
+        <v>7012011</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4054,13 +4070,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730336</t>
+          <t>https://artportalen.se/Sighting/104730081</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>104730419</v>
+        <v>104730336</v>
       </c>
       <c r="B32" t="n">
         <v>79328</v>
@@ -4096,10 +4112,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>609955</v>
+        <v>609883</v>
       </c>
       <c r="R32" t="n">
-        <v>7012162</v>
+        <v>7012110</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4167,13 +4183,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730419</t>
+          <t>https://artportalen.se/Sighting/104730336</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>104730461</v>
+        <v>104730419</v>
       </c>
       <c r="B33" t="n">
         <v>79328</v>
@@ -4209,10 +4225,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>609975</v>
+        <v>609955</v>
       </c>
       <c r="R33" t="n">
-        <v>7012174</v>
+        <v>7012162</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4280,13 +4296,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730461</t>
+          <t>https://artportalen.se/Sighting/104730419</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>104730483</v>
+        <v>104730461</v>
       </c>
       <c r="B34" t="n">
         <v>79328</v>
@@ -4322,10 +4338,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>609999</v>
+        <v>609975</v>
       </c>
       <c r="R34" t="n">
-        <v>7012162</v>
+        <v>7012174</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4393,13 +4409,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104730483</t>
+          <t>https://artportalen.se/Sighting/104730461</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>104730501</v>
+        <v>104730483</v>
       </c>
       <c r="B35" t="n">
         <v>79328</v>
@@ -4435,10 +4451,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>610046</v>
+        <v>609999</v>
       </c>
       <c r="R35" t="n">
-        <v>7012129</v>
+        <v>7012162</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4505,6 +4521,119 @@
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104730483</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>104730501</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>610046</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7012129</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ed</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-11-18</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/104730501</t>
         </is>
@@ -4546,6 +4675,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -2914,7 +2914,7 @@
         <v>137031412</v>
       </c>
       <c r="B22" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>136809946</v>
       </c>
       <c r="B29" t="n">
-        <v>98419</v>
+        <v>98423</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>137031347</v>
       </c>
       <c r="B30" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -3742,7 +3742,7 @@
         <v>136809946</v>
       </c>
       <c r="B29" t="n">
-        <v>98423</v>
+        <v>98425</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -2914,7 +2914,7 @@
         <v>137031412</v>
       </c>
       <c r="B22" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>136809946</v>
       </c>
       <c r="B29" t="n">
-        <v>98425</v>
+        <v>98427</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>137031347</v>
       </c>
       <c r="B30" t="n">
-        <v>79169</v>
+        <v>79172</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -2914,7 +2914,7 @@
         <v>137031412</v>
       </c>
       <c r="B22" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>136809697</v>
       </c>
       <c r="B25" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>137117586</v>
       </c>
       <c r="B26" t="n">
-        <v>58000</v>
+        <v>58013</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>136809946</v>
       </c>
       <c r="B29" t="n">
-        <v>98427</v>
+        <v>98440</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>137031347</v>
       </c>
       <c r="B30" t="n">
-        <v>79172</v>
+        <v>79185</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -2914,7 +2914,7 @@
         <v>137031412</v>
       </c>
       <c r="B22" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>136809697</v>
       </c>
       <c r="B25" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>137117586</v>
       </c>
       <c r="B26" t="n">
-        <v>58013</v>
+        <v>58015</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>136809946</v>
       </c>
       <c r="B29" t="n">
-        <v>98440</v>
+        <v>98442</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
         <v>137031347</v>
       </c>
       <c r="B30" t="n">
-        <v>79185</v>
+        <v>79187</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -3283,11 +3283,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ådalsleden, Ång</t>
@@ -3406,11 +3402,7 @@
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -2914,7 +2914,7 @@
         <v>137031412</v>
       </c>
       <c r="B22" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>136809946</v>
       </c>
       <c r="B29" t="n">
-        <v>98442</v>
+        <v>98445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -2914,7 +2914,7 @@
         <v>137031412</v>
       </c>
       <c r="B22" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>136809697</v>
       </c>
       <c r="B25" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>137117586</v>
       </c>
       <c r="B26" t="n">
-        <v>58015</v>
+        <v>58025</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>136809946</v>
       </c>
       <c r="B29" t="n">
-        <v>98445</v>
+        <v>98455</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>137031347</v>
       </c>
       <c r="B30" t="n">
-        <v>79187</v>
+        <v>79197</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -2914,7 +2914,7 @@
         <v>137031412</v>
       </c>
       <c r="B22" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>136809946</v>
       </c>
       <c r="B29" t="n">
-        <v>98455</v>
+        <v>98456</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -2914,7 +2914,7 @@
         <v>137031412</v>
       </c>
       <c r="B22" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>136809697</v>
       </c>
       <c r="B25" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>137117586</v>
       </c>
       <c r="B26" t="n">
-        <v>58025</v>
+        <v>58026</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>136809946</v>
       </c>
       <c r="B29" t="n">
-        <v>98456</v>
+        <v>98461</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>137031347</v>
       </c>
       <c r="B30" t="n">
-        <v>79197</v>
+        <v>79200</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -2914,7 +2914,7 @@
         <v>137031412</v>
       </c>
       <c r="B22" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>136809946</v>
       </c>
       <c r="B29" t="n">
-        <v>98461</v>
+        <v>98463</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -2914,7 +2914,7 @@
         <v>137031412</v>
       </c>
       <c r="B22" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>136809697</v>
       </c>
       <c r="B25" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>137117586</v>
       </c>
       <c r="B26" t="n">
-        <v>58026</v>
+        <v>58027</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>136809946</v>
       </c>
       <c r="B29" t="n">
-        <v>98463</v>
+        <v>98469</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>137031347</v>
       </c>
       <c r="B30" t="n">
-        <v>79200</v>
+        <v>79205</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -2914,7 +2914,7 @@
         <v>137031412</v>
       </c>
       <c r="B22" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>136809946</v>
       </c>
       <c r="B29" t="n">
-        <v>98469</v>
+        <v>98481</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>137031347</v>
       </c>
       <c r="B30" t="n">
-        <v>79205</v>
+        <v>79216</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -2914,7 +2914,7 @@
         <v>137031412</v>
       </c>
       <c r="B22" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>136809946</v>
       </c>
       <c r="B29" t="n">
-        <v>98481</v>
+        <v>98482</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>137031347</v>
       </c>
       <c r="B30" t="n">
-        <v>79216</v>
+        <v>79217</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -2914,7 +2914,7 @@
         <v>137031412</v>
       </c>
       <c r="B22" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>136809946</v>
       </c>
       <c r="B29" t="n">
-        <v>98482</v>
+        <v>98485</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>137031347</v>
       </c>
       <c r="B30" t="n">
-        <v>79217</v>
+        <v>79219</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -3734,7 +3734,7 @@
         <v>136809946</v>
       </c>
       <c r="B29" t="n">
-        <v>98485</v>
+        <v>98486</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 24887-2022 artfynd.xlsx
+++ b/artfynd/A 24887-2022 artfynd.xlsx
@@ -2914,7 +2914,7 @@
         <v>137031412</v>
       </c>
       <c r="B22" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>137117586</v>
       </c>
       <c r="B26" t="n">
-        <v>58027</v>
+        <v>58030</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3734,7 +3734,7 @@
         <v>136809946</v>
       </c>
       <c r="B29" t="n">
-        <v>98486</v>
+        <v>98489</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>137031347</v>
       </c>
       <c r="B30" t="n">
-        <v>79219</v>
+        <v>79223</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
